--- a/resources/digital-products/files/dp-adv-durability.xlsx
+++ b/resources/digital-products/files/dp-adv-durability.xlsx
@@ -511,7 +511,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -657,5 +657,6 @@
     <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-adv-durability.xlsx
+++ b/resources/digital-products/files/dp-adv-durability.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -554,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -604,6 +606,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -626,6 +629,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -633,6 +637,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
@@ -645,12 +650,17 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
